--- a/data/raw/battle_winners_review.xlsx
+++ b/data/raw/battle_winners_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a162256969a0cf7f/Desktop/Files/Github/project-rap-sheet/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="11_038931A5D3B05B186B1A2511595ED87656C595D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4C27E21-1793-4DA7-91D8-88ECA12A09E9}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="11_038931A5D3B05B186B1A2511595ED87656C595D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48543219-5804-472A-A3D0-233E3F5E5C7C}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6398" uniqueCount="4164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6429" uniqueCount="4165">
   <si>
     <t>title</t>
   </si>
@@ -12512,6 +12512,9 @@
   </si>
   <si>
     <t>9-0</t>
+  </si>
+  <si>
+    <t>age restricted</t>
   </si>
 </sst>
 </file>
@@ -12587,7 +12590,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -14379,7 +14382,7 @@
         <v>4150</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>263</v>
       </c>
@@ -14402,7 +14405,7 @@
         <v>4150</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>267</v>
       </c>
@@ -14425,7 +14428,7 @@
         <v>4158</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>271</v>
       </c>
@@ -14441,8 +14444,14 @@
       <c r="E67" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F67" t="s">
+        <v>213</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>275</v>
       </c>
@@ -14458,8 +14467,14 @@
       <c r="E68" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F68" t="s">
+        <v>274</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>278</v>
       </c>
@@ -14475,8 +14490,14 @@
       <c r="E69" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F69" t="s">
+        <v>274</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>282</v>
       </c>
@@ -14492,8 +14513,14 @@
       <c r="E70" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F70" t="s">
+        <v>274</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>286</v>
       </c>
@@ -14509,8 +14536,14 @@
       <c r="E71" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F71" t="s">
+        <v>71</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>289</v>
       </c>
@@ -14526,8 +14559,14 @@
       <c r="E72" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F72" t="s">
+        <v>292</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>293</v>
       </c>
@@ -14543,8 +14582,11 @@
       <c r="E73" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73" t="s">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>297</v>
       </c>
@@ -14560,8 +14602,14 @@
       <c r="E74" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F74" t="s">
+        <v>274</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>301</v>
       </c>
@@ -14577,8 +14625,14 @@
       <c r="E75" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F75" t="s">
+        <v>304</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>305</v>
       </c>
@@ -14594,8 +14648,14 @@
       <c r="E76" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F76" t="s">
+        <v>274</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>309</v>
       </c>
@@ -14611,8 +14671,14 @@
       <c r="E77" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F77" t="s">
+        <v>145</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>312</v>
       </c>
@@ -14628,8 +14694,14 @@
       <c r="E78" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F78" t="s">
+        <v>315</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>316</v>
       </c>
@@ -14645,8 +14717,14 @@
       <c r="E79" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F79" t="s">
+        <v>319</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>320</v>
       </c>
@@ -14662,8 +14740,14 @@
       <c r="E80" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80" t="s">
+        <v>319</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>324</v>
       </c>
@@ -14679,8 +14763,14 @@
       <c r="E81" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81" t="s">
+        <v>327</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>329</v>
       </c>
@@ -14696,8 +14786,14 @@
       <c r="E82" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82" t="s">
+        <v>327</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>333</v>
       </c>
@@ -14714,7 +14810,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>338</v>
       </c>
@@ -14731,7 +14827,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>342</v>
       </c>
@@ -14748,7 +14844,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>346</v>
       </c>
@@ -14765,7 +14861,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>350</v>
       </c>
@@ -14782,7 +14878,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>354</v>
       </c>
@@ -14799,7 +14895,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>358</v>
       </c>
@@ -14816,7 +14912,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>361</v>
       </c>
@@ -14833,7 +14929,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>365</v>
       </c>
@@ -14850,7 +14946,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>368</v>
       </c>
@@ -14867,7 +14963,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>372</v>
       </c>
@@ -14884,7 +14980,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>376</v>
       </c>
@@ -14901,7 +14997,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>380</v>
       </c>
@@ -14918,7 +15014,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>385</v>
       </c>

--- a/data/raw/battle_winners_review.xlsx
+++ b/data/raw/battle_winners_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a162256969a0cf7f/Desktop/Files/Github/project-rap-sheet/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFDD6A38-6CD1-4AC8-943D-B48790DB1B5C}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34360B36-0470-4C79-87A2-39DF79681314}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6441" uniqueCount="4164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6475" uniqueCount="4166">
   <si>
     <t>title</t>
   </si>
@@ -12512,6 +12512,12 @@
   </si>
   <si>
     <t>notes</t>
+  </si>
+  <si>
+    <t>7-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
   </si>
 </sst>
 </file>
@@ -12593,7 +12599,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -12611,6 +12617,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14944,6 +14954,12 @@
       <c r="E89" t="s">
         <v>356</v>
       </c>
+      <c r="F89" t="s">
+        <v>355</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>4151</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
@@ -14961,6 +14977,12 @@
       <c r="E90" t="s">
         <v>360</v>
       </c>
+      <c r="F90" t="s">
+        <v>360</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>4149</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
@@ -14978,6 +15000,12 @@
       <c r="E91" t="s">
         <v>364</v>
       </c>
+      <c r="F91" t="s">
+        <v>364</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>4152</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -14995,6 +15023,12 @@
       <c r="E92" t="s">
         <v>368</v>
       </c>
+      <c r="F92" t="s">
+        <v>126</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>4151</v>
+      </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
@@ -15012,6 +15046,12 @@
       <c r="E93" t="s">
         <v>372</v>
       </c>
+      <c r="F93" t="s">
+        <v>372</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>4151</v>
+      </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -15029,6 +15069,12 @@
       <c r="E94" t="s">
         <v>376</v>
       </c>
+      <c r="F94" t="s">
+        <v>376</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>4164</v>
+      </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -15046,6 +15092,12 @@
       <c r="E95" t="s">
         <v>256</v>
       </c>
+      <c r="F95" t="s">
+        <v>126</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>4151</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
@@ -15063,8 +15115,14 @@
       <c r="E96" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96" t="s">
+        <v>126</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>384</v>
       </c>
@@ -15080,8 +15138,14 @@
       <c r="E97" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97" t="s">
+        <v>126</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>387</v>
       </c>
@@ -15097,8 +15161,14 @@
       <c r="E98" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98" t="s">
+        <v>390</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>391</v>
       </c>
@@ -15114,8 +15184,14 @@
       <c r="E99" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99" t="s">
+        <v>126</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>395</v>
       </c>
@@ -15131,8 +15207,14 @@
       <c r="E100" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100" t="s">
+        <v>398</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>399</v>
       </c>
@@ -15148,8 +15230,14 @@
       <c r="E101" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101" t="s">
+        <v>403</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>404</v>
       </c>
@@ -15165,8 +15253,14 @@
       <c r="E102" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102" t="s">
+        <v>407</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>408</v>
       </c>
@@ -15182,8 +15276,14 @@
       <c r="E103" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103" t="s">
+        <v>411</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>412</v>
       </c>
@@ -15199,8 +15299,14 @@
       <c r="E104" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104" t="s">
+        <v>415</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>417</v>
       </c>
@@ -15216,8 +15322,14 @@
       <c r="E105" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105" t="s">
+        <v>420</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>421</v>
       </c>
@@ -15234,7 +15346,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>424</v>
       </c>
@@ -15251,7 +15363,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>427</v>
       </c>
@@ -15268,7 +15380,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>430</v>
       </c>
@@ -15285,7 +15397,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>434</v>
       </c>
@@ -15302,7 +15414,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>438</v>
       </c>
@@ -15319,7 +15431,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>441</v>
       </c>

--- a/data/raw/battle_winners_review.xlsx
+++ b/data/raw/battle_winners_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a162256969a0cf7f/Desktop/Files/Github/project-rap-sheet/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34360B36-0470-4C79-87A2-39DF79681314}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{447BA2E5-586B-4FF6-B112-A4D5D6CD513C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6475" uniqueCount="4166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6516" uniqueCount="4168">
   <si>
     <t>title</t>
   </si>
@@ -12518,6 +12518,12 @@
   </si>
   <si>
     <t>4-3</t>
+  </si>
+  <si>
+    <t>3-1-1(NV)</t>
+  </si>
+  <si>
+    <t>NV = no vote</t>
   </si>
 </sst>
 </file>
@@ -15122,7 +15128,7 @@
         <v>4153</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>384</v>
       </c>
@@ -15145,7 +15151,7 @@
         <v>4149</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>387</v>
       </c>
@@ -15168,7 +15174,7 @@
         <v>4151</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>391</v>
       </c>
@@ -15191,7 +15197,7 @@
         <v>4165</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>395</v>
       </c>
@@ -15214,7 +15220,7 @@
         <v>4152</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>399</v>
       </c>
@@ -15237,7 +15243,7 @@
         <v>4150</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>404</v>
       </c>
@@ -15260,7 +15266,7 @@
         <v>4152</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>408</v>
       </c>
@@ -15283,7 +15289,7 @@
         <v>4152</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>412</v>
       </c>
@@ -15306,7 +15312,7 @@
         <v>4155</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>417</v>
       </c>
@@ -15329,7 +15335,7 @@
         <v>4149</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>421</v>
       </c>
@@ -15345,8 +15351,14 @@
       <c r="E106" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F106" t="s">
+        <v>15</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>424</v>
       </c>
@@ -15362,8 +15374,17 @@
       <c r="E107" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F107" t="s">
+        <v>130</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>4166</v>
+      </c>
+      <c r="H107" t="s">
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>427</v>
       </c>
@@ -15379,8 +15400,14 @@
       <c r="E108" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F108" t="s">
+        <v>49</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>430</v>
       </c>
@@ -15396,8 +15423,14 @@
       <c r="E109" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F109" t="s">
+        <v>130</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>434</v>
       </c>
@@ -15413,8 +15446,14 @@
       <c r="E110" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F110" t="s">
+        <v>437</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>438</v>
       </c>
@@ -15430,8 +15469,14 @@
       <c r="E111" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F111" t="s">
+        <v>376</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>441</v>
       </c>
@@ -15447,8 +15492,14 @@
       <c r="E112" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F112" t="s">
+        <v>130</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>445</v>
       </c>
@@ -15464,8 +15515,14 @@
       <c r="E113" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F113" t="s">
+        <v>130</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>448</v>
       </c>
@@ -15481,8 +15538,14 @@
       <c r="E114" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F114" t="s">
+        <v>130</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>452</v>
       </c>
@@ -15498,8 +15561,14 @@
       <c r="E115" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115" t="s">
+        <v>130</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>456</v>
       </c>
@@ -15515,8 +15584,14 @@
       <c r="E116" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116" t="s">
+        <v>130</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>460</v>
       </c>
@@ -15532,8 +15607,14 @@
       <c r="E117" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F117" t="s">
+        <v>130</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>464</v>
       </c>
@@ -15549,8 +15630,14 @@
       <c r="E118" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F118" t="s">
+        <v>130</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>467</v>
       </c>
@@ -15566,8 +15653,14 @@
       <c r="E119" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F119" t="s">
+        <v>130</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>470</v>
       </c>
@@ -15583,8 +15676,14 @@
       <c r="E120" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120" t="s">
+        <v>93</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>473</v>
       </c>
@@ -15600,8 +15699,14 @@
       <c r="E121" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F121" t="s">
+        <v>130</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>476</v>
       </c>
@@ -15617,8 +15722,14 @@
       <c r="E122" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122" t="s">
+        <v>281</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>479</v>
       </c>
@@ -15634,8 +15745,14 @@
       <c r="E123" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123" t="s">
+        <v>130</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>483</v>
       </c>
@@ -15651,8 +15768,14 @@
       <c r="E124" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124" t="s">
+        <v>130</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>487</v>
       </c>
@@ -15668,8 +15791,14 @@
       <c r="E125" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125" t="s">
+        <v>130</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>490</v>
       </c>
@@ -15686,7 +15815,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>494</v>
       </c>
@@ -15703,7 +15832,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>497</v>
       </c>

--- a/data/raw/battle_winners_review.xlsx
+++ b/data/raw/battle_winners_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a162256969a0cf7f/Desktop/Files/Github/project-rap-sheet/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{447BA2E5-586B-4FF6-B112-A4D5D6CD513C}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E571762-5D7B-4118-82DF-16D6A08735E5}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6516" uniqueCount="4168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6553" uniqueCount="4169">
   <si>
     <t>title</t>
   </si>
@@ -12524,6 +12524,9 @@
   </si>
   <si>
     <t>NV = no vote</t>
+  </si>
+  <si>
+    <t>no 5th judge; crowd cheer used as last judge</t>
   </si>
 </sst>
 </file>
@@ -15814,6 +15817,12 @@
       <c r="E126" t="s">
         <v>209</v>
       </c>
+      <c r="F126" t="s">
+        <v>209</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>4149</v>
+      </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
@@ -15831,6 +15840,12 @@
       <c r="E127" t="s">
         <v>210</v>
       </c>
+      <c r="F127" t="s">
+        <v>493</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>4149</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
@@ -15848,8 +15863,14 @@
       <c r="E128" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128" t="s">
+        <v>176</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>501</v>
       </c>
@@ -15865,8 +15886,14 @@
       <c r="E129" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129" t="s">
+        <v>97</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>4159</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>504</v>
       </c>
@@ -15882,8 +15909,17 @@
       <c r="E130" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130" t="s">
+        <v>176</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>4149</v>
+      </c>
+      <c r="H130" t="s">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>508</v>
       </c>
@@ -15899,8 +15935,14 @@
       <c r="E131" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131" t="s">
+        <v>61</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>511</v>
       </c>
@@ -15916,8 +15958,14 @@
       <c r="E132" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132" t="s">
+        <v>176</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>514</v>
       </c>
@@ -15933,8 +15981,14 @@
       <c r="E133" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133" t="s">
+        <v>517</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>518</v>
       </c>
@@ -15950,8 +16004,14 @@
       <c r="E134" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134" t="s">
+        <v>521</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>522</v>
       </c>
@@ -15967,8 +16027,14 @@
       <c r="E135" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135" t="s">
+        <v>245</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>526</v>
       </c>
@@ -15984,8 +16050,14 @@
       <c r="E136" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136" t="s">
+        <v>245</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>529</v>
       </c>
@@ -16001,8 +16073,14 @@
       <c r="E137" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137" t="s">
+        <v>532</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>533</v>
       </c>
@@ -16018,8 +16096,14 @@
       <c r="E138" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138" t="s">
+        <v>536</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>537</v>
       </c>
@@ -16035,8 +16119,14 @@
       <c r="E139" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139" t="s">
+        <v>540</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>541</v>
       </c>
@@ -16052,8 +16142,14 @@
       <c r="E140" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140" t="s">
+        <v>544</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>545</v>
       </c>
@@ -16069,8 +16165,14 @@
       <c r="E141" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141" t="s">
+        <v>548</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>549</v>
       </c>
@@ -16086,8 +16188,14 @@
       <c r="E142" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142" t="s">
+        <v>548</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>553</v>
       </c>
@@ -16103,8 +16211,14 @@
       <c r="E143" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143" t="s">
+        <v>548</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>557</v>
       </c>

--- a/data/raw/battle_winners_review.xlsx
+++ b/data/raw/battle_winners_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a162256969a0cf7f/Desktop/Files/Github/project-rap-sheet/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E571762-5D7B-4118-82DF-16D6A08735E5}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E56236-4108-4B19-96E0-2BB139407EB0}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6553" uniqueCount="4169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6586" uniqueCount="4171">
   <si>
     <t>title</t>
   </si>
@@ -12527,6 +12527,12 @@
   </si>
   <si>
     <t>no 5th judge; crowd cheer used as last judge</t>
+  </si>
+  <si>
+    <t>5-0-0(OT)</t>
+  </si>
+  <si>
+    <t>5 votes for BR after OT; no indication of what the vote was befor OT</t>
   </si>
 </sst>
 </file>
@@ -16234,8 +16240,14 @@
       <c r="E144" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144" t="s">
+        <v>561</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>562</v>
       </c>
@@ -16251,8 +16263,14 @@
       <c r="E145" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145" t="s">
+        <v>565</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>566</v>
       </c>
@@ -16268,8 +16286,14 @@
       <c r="E146" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F146" t="s">
+        <v>560</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>570</v>
       </c>
@@ -16285,8 +16309,14 @@
       <c r="E147" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147" t="s">
+        <v>134</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>573</v>
       </c>
@@ -16302,8 +16332,14 @@
       <c r="E148" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148" t="s">
+        <v>134</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>576</v>
       </c>
@@ -16319,8 +16355,14 @@
       <c r="E149" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149" t="s">
+        <v>134</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>579</v>
       </c>
@@ -16336,8 +16378,14 @@
       <c r="E150" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150" t="s">
+        <v>252</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>582</v>
       </c>
@@ -16353,8 +16401,14 @@
       <c r="E151" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151" t="s">
+        <v>134</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>586</v>
       </c>
@@ -16370,8 +16424,17 @@
       <c r="E152" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152" t="s">
+        <v>134</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>4169</v>
+      </c>
+      <c r="H152" t="s">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>589</v>
       </c>
@@ -16387,8 +16450,14 @@
       <c r="E153" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F153" t="s">
+        <v>592</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>593</v>
       </c>
@@ -16404,8 +16473,14 @@
       <c r="E154" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154" t="s">
+        <v>134</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>596</v>
       </c>
@@ -16421,8 +16496,14 @@
       <c r="E155" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F155" t="s">
+        <v>134</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>599</v>
       </c>
@@ -16438,8 +16519,14 @@
       <c r="E156" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156" t="s">
+        <v>134</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>603</v>
       </c>
@@ -16455,8 +16542,14 @@
       <c r="E157" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F157" t="s">
+        <v>89</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>606</v>
       </c>
@@ -16472,8 +16565,14 @@
       <c r="E158" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F158" t="s">
+        <v>134</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>609</v>
       </c>
@@ -16489,8 +16588,14 @@
       <c r="E159" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F159" t="s">
+        <v>612</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>613</v>
       </c>

--- a/data/raw/battle_winners_review.xlsx
+++ b/data/raw/battle_winners_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a162256969a0cf7f/Desktop/Files/Github/project-rap-sheet/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E56236-4108-4B19-96E0-2BB139407EB0}"/>
+  <xr:revisionPtr revIDLastSave="318" documentId="11_3BE9D1A4D360532EA3FB3F11595ED87656C505C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A08D6BE-0FBE-41EE-A24B-0D17F8D03BB9}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6586" uniqueCount="4171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6658" uniqueCount="4173">
   <si>
     <t>title</t>
   </si>
@@ -12532,7 +12532,13 @@
     <t>5-0-0(OT)</t>
   </si>
   <si>
-    <t>5 votes for BR after OT; no indication of what the vote was befor OT</t>
+    <t>No judging in footage</t>
+  </si>
+  <si>
+    <t>8-0</t>
+  </si>
+  <si>
+    <t>5 votes for BR after OT; no indication of what the vote was before OT</t>
   </si>
 </sst>
 </file>
@@ -16431,7 +16437,7 @@
         <v>4169</v>
       </c>
       <c r="H152" t="s">
-        <v>4170</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -16611,8 +16617,14 @@
       <c r="E160" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F160" t="s">
+        <v>616</v>
+      </c>
+      <c r="H160" t="s">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>617</v>
       </c>
@@ -16628,8 +16640,14 @@
       <c r="E161" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F161" t="s">
+        <v>616</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>620</v>
       </c>
@@ -16645,8 +16663,14 @@
       <c r="E162" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F162" t="s">
+        <v>616</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>623</v>
       </c>
@@ -16662,8 +16686,14 @@
       <c r="E163" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F163" t="s">
+        <v>616</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>627</v>
       </c>
@@ -16679,8 +16709,14 @@
       <c r="E164" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F164" t="s">
+        <v>616</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>631</v>
       </c>
@@ -16696,8 +16732,14 @@
       <c r="E165" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F165" t="s">
+        <v>376</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>634</v>
       </c>
@@ -16713,8 +16755,14 @@
       <c r="E166" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F166" t="s">
+        <v>616</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>638</v>
       </c>
@@ -16730,8 +16778,14 @@
       <c r="E167" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F167" t="s">
+        <v>616</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>642</v>
       </c>
@@ -16747,8 +16801,14 @@
       <c r="E168" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F168" t="s">
+        <v>616</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>645</v>
       </c>
@@ -16764,8 +16824,14 @@
       <c r="E169" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F169" t="s">
+        <v>648</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>649</v>
       </c>
@@ -16781,8 +16847,14 @@
       <c r="E170" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F170" t="s">
+        <v>616</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>652</v>
       </c>
@@ -16798,8 +16870,14 @@
       <c r="E171" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F171" t="s">
+        <v>270</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>655</v>
       </c>
@@ -16815,8 +16893,14 @@
       <c r="E172" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F172" t="s">
+        <v>616</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>658</v>
       </c>
@@ -16832,8 +16916,14 @@
       <c r="E173" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F173" t="s">
+        <v>97</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>661</v>
       </c>
@@ -16849,8 +16939,14 @@
       <c r="E174" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F174" t="s">
+        <v>616</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>664</v>
       </c>
@@ -16866,8 +16962,14 @@
       <c r="E175" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F175" t="s">
+        <v>616</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>668</v>
       </c>
@@ -16883,8 +16985,14 @@
       <c r="E176" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F176" t="s">
+        <v>616</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>671</v>
       </c>
@@ -16900,8 +17008,14 @@
       <c r="E177" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F177" t="s">
+        <v>616</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>4171</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>674</v>
       </c>
@@ -16917,8 +17031,14 @@
       <c r="E178" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F178" t="s">
+        <v>616</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>677</v>
       </c>
@@ -16934,8 +17054,14 @@
       <c r="E179" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F179" t="s">
+        <v>315</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>680</v>
       </c>
@@ -16951,8 +17077,14 @@
       <c r="E180" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F180" t="s">
+        <v>616</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>683</v>
       </c>
@@ -16968,8 +17100,14 @@
       <c r="E181" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F181" t="s">
+        <v>616</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>687</v>
       </c>
@@ -16985,8 +17123,14 @@
       <c r="E182" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F182" t="s">
+        <v>616</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>690</v>
       </c>
@@ -17002,8 +17146,14 @@
       <c r="E183" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F183" t="s">
+        <v>612</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>693</v>
       </c>
@@ -17019,8 +17169,14 @@
       <c r="E184" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F184" t="s">
+        <v>616</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>696</v>
       </c>
@@ -17036,8 +17192,14 @@
       <c r="E185" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F185" t="s">
+        <v>700</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>701</v>
       </c>
@@ -17053,8 +17215,14 @@
       <c r="E186" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F186" t="s">
+        <v>704</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>705</v>
       </c>
@@ -17070,8 +17238,14 @@
       <c r="E187" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F187" t="s">
+        <v>704</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>709</v>
       </c>
@@ -17087,8 +17261,14 @@
       <c r="E188" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F188" t="s">
+        <v>712</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>713</v>
       </c>
@@ -17104,8 +17284,14 @@
       <c r="E189" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F189" t="s">
+        <v>716</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>717</v>
       </c>
@@ -17121,8 +17307,14 @@
       <c r="E190" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F190" t="s">
+        <v>41</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>721</v>
       </c>
@@ -17138,8 +17330,14 @@
       <c r="E191" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F191" t="s">
+        <v>41</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>725</v>
       </c>
@@ -17155,8 +17353,14 @@
       <c r="E192" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F192" t="s">
+        <v>729</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>730</v>
       </c>
@@ -17172,8 +17376,14 @@
       <c r="E193" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F193" t="s">
+        <v>728</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>733</v>
       </c>
@@ -17189,8 +17399,14 @@
       <c r="E194" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F194" t="s">
+        <v>736</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>737</v>
       </c>
@@ -17206,8 +17422,14 @@
       <c r="E195" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F195" t="s">
+        <v>740</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>742</v>
       </c>
@@ -17224,7 +17446,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>746</v>
       </c>
@@ -17241,7 +17463,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>750</v>
       </c>
@@ -17258,7 +17480,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>753</v>
       </c>
@@ -17275,7 +17497,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>756</v>
       </c>
@@ -17292,7 +17514,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>759</v>
       </c>
@@ -17309,7 +17531,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>762</v>
       </c>
@@ -17326,7 +17548,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>766</v>
       </c>
@@ -17343,7 +17565,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>768</v>
       </c>
@@ -17360,7 +17582,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>771</v>
       </c>
@@ -17377,7 +17599,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>774</v>
       </c>
@@ -17394,7 +17616,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>777</v>
       </c>
@@ -17411,7 +17633,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>781</v>
       </c>
